--- a/important_mails_2026-06-05.xlsx
+++ b/important_mails_2026-06-05.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H209"/>
+  <dimension ref="A1:H207"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -500,21 +500,71 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Fri, 5 Jun 2026 03:06:03 +0000</t>
+          <t>Fri, 5 Jun 2026 19:25:12 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.com Inventory</t>
+          <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 5 Jun 2026 03:06:03 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.com Inventory</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -534,39 +584,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 13:05:07 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -596,39 +646,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:43:35 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -653,39 +703,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:33:36 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.se Faktura Fraktas Av Amazon for 5/2026
  96
@@ -712,39 +762,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:16:55 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -762,39 +812,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:09:15 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 5/2026</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 5/2026
  96
@@ -812,39 +862,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 12:09:08 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.nl Factuur Fulfilled by Amazon for 5/2026
  96
@@ -868,39 +918,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 11:58:55 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.de Rechnung Versand durch Amazon for 5/2026
  96
@@ -925,39 +975,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Fri, 5 Jun 2026 11:38:44 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.es Factura Logística de Amazon for 5/2026
  96
@@ -984,39 +1034,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 05:07:33 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (MtDohxu3JK)</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1036,39 +1086,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 13:57:10 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (okvedC6bat)</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1088,39 +1138,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 08:40:44 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1136,39 +1186,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 19:29:32 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (260520getf)</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1193,39 +1243,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:43:35 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $143.78 in an attempt to settle your Amazon seller account balance.
@@ -1241,39 +1291,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 01:13:32 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq5h330940)</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1298,39 +1348,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 15:15:46 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1350,39 +1400,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1399,39 +1449,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 14:58:44 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1451,39 +1501,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:36 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1503,39 +1553,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:55:10 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1555,39 +1605,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 14:37:25 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1604,39 +1654,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 23:31:40 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1656,39 +1706,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:23:36 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1706,39 +1756,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:17:04 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1756,39 +1806,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:40:15 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1804,39 +1854,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:33:38 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1855,39 +1905,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 21:10:43 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1905,39 +1955,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:18:22 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -1955,39 +2005,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:12:35 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2005,39 +2055,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 02:36:04 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"compliance-ops-mass-programs@amazon.com" &lt;compliance-ops-mass-programs@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12662433092] 通过亚马逊完成奥地利EPR注册
@@ -2072,39 +2122,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 2 Jun 2026 12:53:21 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -2120,40 +2170,40 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 10:39:43 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.se" &lt;cscompliance-docreview-seller@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A2NODRKZP88ZB9 - SPO - Seller Partner Outreach - Document Review
@@ -2170,40 +2220,40 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 14:31:42 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS -
  APPEAL</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - PS - APPEAL
@@ -2224,39 +2274,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:48 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2274,39 +2324,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:09:04 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2324,60 +2374,10 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 29 May 2026 16:10:43 +0000</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Fri, 29 May 2026 16:07:21 +0000</t>
+          <t>Thu, 4 Jun 2026 23:11:17 +0000</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -2402,62 +2402,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to reactivate listings</t>
+          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
+ le offerte</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
       <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai EU,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listing?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 4 Jun 2026 23:11:17 +0000</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
- le offerte</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -2473,40 +2423,40 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 23:10:46 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -2522,39 +2472,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:37:38 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -2593,39 +2543,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:31:54 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -2641,39 +2591,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:14:06 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -2689,39 +2639,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 19:10:02 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -2737,40 +2687,40 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:43:42 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -2785,40 +2735,40 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:42:40 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -2832,39 +2782,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:38:41 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -2878,39 +2828,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:37:16 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -2925,39 +2875,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:35:16 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -2971,39 +2921,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:31:58 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -3018,39 +2968,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:35:34 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -3089,39 +3039,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:29:07 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -3137,40 +3087,40 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:25:02 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -3186,39 +3136,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:15:34 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -3232,39 +3182,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:12:56 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -3280,40 +3230,40 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:12:34 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -3329,39 +3279,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 19:09:18 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -3377,39 +3327,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3424,39 +3374,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Wed, 3 Jun 2026 13:54:47 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -3471,39 +3421,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 16:55:18 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>Logística Multicanal de Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Ahorra un 20 % en las tarifas de Logística Multicanal a partir del 25 de junio</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
  Ya están disponibles dos nuevos programas de descuentos para los vendedores aptos
@@ -3517,39 +3467,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 16:38:54 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale di Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>Tariffe di Gestione multicanale: sconto del 20% dal 25 giugno</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
  Due nuovi programmi di sconto sono ora disponibili per i venditori idonei
@@ -3563,39 +3513,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 02:40:59 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 05/2026</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -3613,39 +3563,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:40 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -3661,39 +3611,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:32 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -3707,40 +3657,40 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:11:31 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -3756,39 +3706,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 16:08:15 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -3804,40 +3754,40 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 15:14:09 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -3853,39 +3803,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 15:14:03 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -3901,230 +3851,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 29 May 2026 16:10:04 +0000</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>96
- Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
- Hej Weihai EU!
- Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
- Varför händer det här?
- Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
- Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
- Hur återaktiverar jag mina produktposter?
- Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
--
- Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 29 May 2026 16:10:01 +0000</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
- Dzień dobry Weihai EU,
- niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
- Dlaczego tak się stało?
- Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
- Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
- Jak mogę ponownie aktywować oferty?
- Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 29 May 2026 16:10:00 +0000</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
- le offerte</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>96
- Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
- Gentile Weihai EU,
- Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
- Ciò a cosa è dovuto?
- Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
- La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
- Come faccio a riattivare le mie offerte?
- Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
--
- Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 29 May 2026 16:07:29 +0000</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>96
- Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
- Bonjour Weihai EU,
- Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
- Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
- Comment réactiver mes produits mis en vente ?
- Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
--
- Si vous disposez des documents requis, suivez les instructio</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sun, 31 May 2026 20:10:01 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -4140,39 +3899,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 04:57:03 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-06-11</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -4195,39 +3954,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 03:41:21 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -4251,39 +4010,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Sat, 30 May 2026 03:00:56 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -4306,39 +4065,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Thu, 4 Jun 2026 12:46:25 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -4392,39 +4151,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Mon, 1 Jun 2026 00:17:48 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -4454,39 +4213,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 06:55:02 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (7kDrHSJf1h)</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4506,39 +4265,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 03:26:42 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4554,39 +4313,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 13:57:34 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Iot4D83CtY)</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4606,39 +4365,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 02:44:04 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (y8kVKdPDvp)</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4658,39 +4417,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:33:15 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
@@ -4706,39 +4465,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -4764,39 +4523,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4812,39 +4571,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Sun, 10 May 2026 16:45:41 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (Xq4e6nl040)</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4869,39 +4628,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 05:42:00 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (zl4CmeMn1C)</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4921,39 +4680,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 18:10:42 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (toabAY9R4I)</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -4973,39 +4732,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 11:59:35 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (cp3IU6ppnV)</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -5025,39 +4784,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 16:07:01 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -5078,39 +4837,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:43:44 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5130,39 +4889,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Fri, 29 May 2026 14:42:27 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5182,39 +4941,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 14:51:20 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -5230,39 +4989,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 13:35:40 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5279,39 +5038,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 14:39:47 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5331,39 +5090,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:30:35 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5383,39 +5142,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 15:29:45 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5432,39 +5191,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Thu, 21 May 2026 14:22:00 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5484,39 +5243,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Wed, 20 May 2026 13:54:11 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5536,39 +5295,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:21:19 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January - March 2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -5585,39 +5344,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 15:07:05 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for January-March 2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -5634,39 +5393,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 14:48:57 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5686,39 +5445,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:42 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -5742,39 +5501,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 11:16:19 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -5798,39 +5557,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 13:46:45 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5850,39 +5609,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:49:45 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5902,39 +5661,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5954,39 +5713,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 15:36:52 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6006,39 +5765,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:51:22 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -6054,39 +5813,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:50:04 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6103,39 +5862,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 14:49:55 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6155,39 +5914,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Wed, 13 May 2026 14:53:51 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -6204,39 +5963,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:42 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6253,39 +6012,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:03:28 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6305,39 +6064,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Thu, 7 May 2026 15:01:21 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6357,39 +6116,139 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 16:10:43 +0000</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 16:07:21 +0000</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai EU,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listing?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subj</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Thu, 28 May 2026 06:06:12 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>帮您免费一站式搞定VAT、EPR等合规问题！亚马逊合规服务商城现已正式上线！</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>亚马逊合规服务商城正式上线，一站式帮助卖家高效搞定欧洲站点的VAT、EPR等合规问题。
 			尊敬的 深圳市微海众信科技有限公司,
@@ -6419,39 +6278,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 17:40:38 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -6470,40 +6329,40 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Wed, 27 May 2026 11:02:38 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ, MARKETPLACE: 1 - PS - APPEAL
@@ -6516,40 +6375,40 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:58:41 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.ca" &lt;cscompliance-docreview-vendor@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 7 - CSC - DOC REVIEW
@@ -6566,40 +6425,40 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:53:39 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC - DOC REVIEW
@@ -6616,40 +6475,40 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:49:38 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC - DOC REVIEW
@@ -6666,39 +6525,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 03:02:52 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -6718,40 +6577,40 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:57:24 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -6767,40 +6626,40 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Mon, 25 May 2026 02:55:04 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.fr" &lt;cscompliance-docreview-seller@amazon.fr&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE: A13V1IB3VIYZZH - SPO - Seller Partner Outreach - Document Review
@@ -6816,39 +6675,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Tue, 19 May 2026 17:11:27 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -6867,40 +6726,40 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:24:17 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -6916,40 +6775,40 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:03:38 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0DD7R3PPG, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -6963,40 +6822,40 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Mon, 18 May 2026 07:02:28 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.it" &lt;cscompliance-docreview-seller@amazon.it&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  APJ6JRA9NG5V4 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -7010,40 +6869,40 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -7056,39 +6915,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -7108,39 +6967,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 15 May 2026 07:42:16 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-de@amazon.com" &lt;fba-3p-buyability-improvement-de@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -7165,39 +7024,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 10:44:21 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-it@amazon.com" &lt;fba-3p-buyability-improvement-it@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>主题：需要采取的行动：网站禁止的 ASIN</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，
 我们与您联系是为了让您知道，由于您的某些 ASIN 被禁止显示，您可能会错失销售机会.
@@ -7222,40 +7081,40 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:51 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.com" &lt;cscompliance-docreview-seller@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 1 - CSC -
  DOC REVIEW</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -7270,40 +7129,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:19:28 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-vendor@amazon.com.mx" &lt;cscompliance-docreview-vendor@amazon.com.mx&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>SELLER: A192R36HNXVJ38, ASIN: B0FCDRNTT8, MARKETPLACE: 771770 - CSC
  - DOC REVIEW</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -7317,40 +7176,40 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 09:15:37 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0G6XCTGJC, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>Do not reply back to this e-mail!
 Hello,
@@ -7364,41 +7223,41 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:37:14 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour
  les ventes sur Amazon.fr |   Your VAT invoice for EPR Pay on Behalf charges
  for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>Bonjour,
 Votre facture pour couvrant les frais de paiement au titre de la Responsabilité élargie du producteur (REP) pour les ventes sur Amazon.fr est désormais disponible.
@@ -7409,10 +7268,153 @@
         </is>
       </c>
     </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 16:10:04 +0000</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
+ Hej Weihai EU!
+ Vissa av dina produktposter har inaktiverats på grund av att det saknas obligatorisk överensstämmelse för dina produkter. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
+ Varför händer det här?
+ Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer. Vi har använt oss av både automatiserade metoder och mänskliga expertgranskare för att identifiera problemet och fatta det här beslutet.
+ Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
+ Hur återaktiverar jag mina produktposter?
+ Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
+-
+ Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna. Vi återaktiverar endast produkter som u</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 16:10:01 +0000</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
+ Dzień dobry Weihai EU,
+ niektóre z Twoich ofert zostały zdezaktywowane z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
+ Dlaczego tak się stało?
+ Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami . Do identyfikacji problemu i podjęcia decyzji wykorzystaliśmy zautomatyzowane narzędzia, a otrzymane za ich pomocą wyniki poddaliśmy weryfikacji przez eksperta.
+ Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
+ Jak mogę ponownie aktywować oferty?
+ Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i </t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 29 May 2026 16:10:00 +0000</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
+ le offerte</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
+ Gentile Weihai EU,
+ Alcune delle tue offerte sono state disattivate a causa della mancanza di alcuni requisiti di conformità obbligatori per i tuoi prodotti. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
+ Ciò a cosa è dovuto?
+ Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili. Questa decisione è stata presa sulla base dei risultati di un'analisi effettuata in parte tramite revisione umana e in parte per mezzo di sistemi automatizzati.
+ La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
+ Come faccio a riattivare le mie offerte?
+ Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
+-
+ Se disponi della documentazione richiesta, segui le istruzioni per inviare i do</t>
+        </is>
+      </c>
+    </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -7427,36 +7429,33 @@
       </c>
       <c r="D137" s="2" t="inlineStr">
         <is>
-          <t>Tue, 5 May 2026 17:50:39 +0000</t>
+          <t>Fri, 29 May 2026 16:07:29 +0000</t>
         </is>
       </c>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
+          <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr"/>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Dear Weihai US,
-We have recently restricted listings for the product(s) listed below on Amazon.com.
-Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 06/03/2026), we may dispose of it in accordance with FBA policies.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0DRTR7GYJ
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
-SPC-USAmazon-1583298956134227</t>
+          <t>96
+ Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
+ Bonjour Weihai EU,
+ Certaines de vos mises en vente ont été désactivées, car vos produits ne respectaient pas des exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
+ Pourquoi cela se produit-il ?
+ Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables. Nous nous sommes appuyés sur une combinaison de moyens automatisés et de contrôles menés par des personnes expérimentées pour identifier ce problème et prendre cette décision.
+ Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
+ Comment réactiver mes produits mis en vente ?
+ Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
+-
+ Si vous disposez des documents requis, suivez les instructio</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10489,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -10505,119 +10504,21 @@
       </c>
       <c r="D199" s="2" t="inlineStr">
         <is>
-          <t>Wed, 6 May 2026 15:00:42 +0000</t>
+          <t>Sat, 23 May 2026 04:06:08 +0000</t>
         </is>
       </c>
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
-          <t>Votre paiement est en cours</t>
+          <t>Create FBA removal order by 2026-06-04</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr"/>
       <c r="H199" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Félicitations ! Votre paiement est en cours et arrivera sous peu.
- Tentative de versement
-Félicitations, Weihai EU ! Votre paiement est en cours et arrivera sous trois à cinq jours.
-Le 05/06/26 15:00 CEST, nous avons effectué un virement d’un montant de €
- 110.91 sur le compte lié à votre méthode de paiement (compte bancaire se terminant par 229).
- Si le montant est inférieur au montant auquel vous vous attendiez, voici quelques questions à vous poser :
- Disposez-vous d’un solde de fonds non disponibles ? Amazon peut réserver des fonds afin de couvrir des retours, des réclamations ou des rétrofacturations potentiels des acheteurs. Si tel est le cas, le solde de fin de période de votre rapport sur les paiements affichera le solde des fonds non disponibles réservé.
- Vos ventes couvraient-elles l’ensemble des frais et des retours pour cette période de règlements ? Le montant du paiement reflète votre activité commerciale, les frais de vente et les frais relatifs aux promotions et aux services. Nous vous recommandons de consulter votre rapport sur les paiements sous l’onglet Rapports de Seller Central pour comprendre votre solde de fin de p</t>
-        </is>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B200" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C200" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D200" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 6 May 2026 14:24:59 +0000</t>
-        </is>
-      </c>
-      <c r="E200" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F200" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
-        </is>
-      </c>
-      <c r="G200" s="2" t="inlineStr"/>
-      <c r="H200" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.ae
- عزيزي Shen zhen shi wei hai zhong xin ke ji you xian،
-نراسلك لإبلاغك بأن فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاص بك لشهر 4/2026 متاح الآن في حساب Seller Central الخاص بك.
-للوصول إلى فاتورة الخاص بك، انتقل إلى حساب Seller Central الخاص بك &gt; التقارير &gt; مكتبة المستندات الضريبية &gt; فواتير ضريبة رسم البائع.
-في حساب Seller Central الخاص بك، ستتمكن من عرض {documentType}$ الخاص بك أو تنزيله أو طباعته.
-إذا كانت لديك أي أسئلة، فالمرجو التواصل مع دعم البائع.
- مع أطيب التحيات،
-Amazon.ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B201" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C201" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D201" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 23 May 2026 04:06:08 +0000</t>
-        </is>
-      </c>
-      <c r="E201" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F201" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-06-04</t>
-        </is>
-      </c>
-      <c r="G201" s="2" t="inlineStr"/>
-      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -10640,39 +10541,39 @@
         </is>
       </c>
     </row>
-    <row r="202">
-      <c r="A202" s="2" t="inlineStr">
+    <row r="200">
+      <c r="A200" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B202" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C202" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C200" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
         <is>
           <t>Sat, 23 May 2026 03:17:21 +0000</t>
         </is>
       </c>
-      <c r="E202" s="2" t="inlineStr">
+      <c r="E200" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F202" s="2" t="inlineStr">
+      <c r="F200" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr"/>
-      <c r="H202" s="2" t="inlineStr">
+      <c r="G200" s="2" t="inlineStr"/>
+      <c r="H200" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -10696,39 +10597,39 @@
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="201">
+      <c r="A201" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C203" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="B201" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C201" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
-      <c r="E203" s="2" t="inlineStr">
+      <c r="E201" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F203" s="2" t="inlineStr">
+      <c r="F201" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G203" s="2" t="inlineStr"/>
-      <c r="H203" s="2" t="inlineStr">
+      <c r="G201" s="2" t="inlineStr"/>
+      <c r="H201" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -10752,39 +10653,39 @@
         </is>
       </c>
     </row>
-    <row r="204">
-      <c r="A204" s="2" t="inlineStr">
+    <row r="202">
+      <c r="A202" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B204" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C204" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D204" s="2" t="inlineStr">
+      <c r="B202" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C202" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E204" s="2" t="inlineStr">
+      <c r="E202" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F204" s="2" t="inlineStr">
+      <c r="F202" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G204" s="2" t="inlineStr"/>
-      <c r="H204" s="2" t="inlineStr">
+      <c r="G202" s="2" t="inlineStr"/>
+      <c r="H202" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -10805,39 +10706,39 @@
         </is>
       </c>
     </row>
-    <row r="205">
-      <c r="A205" s="2" t="inlineStr">
+    <row r="203">
+      <c r="A203" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B205" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C205" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D205" s="2" t="inlineStr">
+      <c r="B203" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C203" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E205" s="2" t="inlineStr">
+      <c r="E203" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F205" s="2" t="inlineStr">
+      <c r="F203" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G205" s="2" t="inlineStr"/>
-      <c r="H205" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr"/>
+      <c r="H203" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -10860,39 +10761,39 @@
         </is>
       </c>
     </row>
-    <row r="206">
-      <c r="A206" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B206" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C206" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D206" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C204" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E206" s="2" t="inlineStr">
+      <c r="E204" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F206" s="2" t="inlineStr">
+      <c r="F204" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr"/>
-      <c r="H206" s="2" t="inlineStr">
+      <c r="G204" s="2" t="inlineStr"/>
+      <c r="H204" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -10916,39 +10817,39 @@
         </is>
       </c>
     </row>
-    <row r="207">
-      <c r="A207" s="2" t="inlineStr">
+    <row r="205">
+      <c r="A205" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B207" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C207" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D207" s="2" t="inlineStr">
+      <c r="B205" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C205" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E207" s="2" t="inlineStr">
+      <c r="E205" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F207" s="2" t="inlineStr">
+      <c r="F205" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G207" s="2" t="inlineStr"/>
-      <c r="H207" s="2" t="inlineStr">
+      <c r="G205" s="2" t="inlineStr"/>
+      <c r="H205" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -10971,40 +10872,40 @@
         </is>
       </c>
     </row>
-    <row r="208">
-      <c r="A208" s="2" t="inlineStr">
+    <row r="206">
+      <c r="A206" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B208" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C208" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D208" s="2" t="inlineStr">
+      <c r="B206" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C206" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
         <is>
           <t>Fri, 22 May 2026 07:25:40 +0000</t>
         </is>
       </c>
-      <c r="E208" s="2" t="inlineStr">
+      <c r="E206" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F208" s="2" t="inlineStr">
+      <c r="F206" s="2" t="inlineStr">
         <is>
           <t>Update VAT registration information to reinstate Inventory and FBA
  functionality of your Amazon.it store</t>
         </is>
       </c>
-      <c r="G208" s="2" t="inlineStr"/>
-      <c r="H208" s="2" t="inlineStr">
+      <c r="G206" s="2" t="inlineStr"/>
+      <c r="H206" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -11020,39 +10921,39 @@
         </is>
       </c>
     </row>
-    <row r="209">
-      <c r="A209" s="2" t="inlineStr">
+    <row r="207">
+      <c r="A207" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B209" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C209" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
+      <c r="B207" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C207" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E209" s="2" t="inlineStr">
+      <c r="E207" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F209" s="2" t="inlineStr">
+      <c r="F207" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G209" s="2" t="inlineStr"/>
-      <c r="H209" s="2" t="inlineStr">
+      <c r="G207" s="2" t="inlineStr"/>
+      <c r="H207" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
